--- a/data/semanas/321_pe.xlsx
+++ b/data/semanas/321_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,7 +629,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17084071</v>
+        <v>17097215</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>422 VILA TORRES PE</t>
+          <t>418 - CENTRO 4 -PE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rua TIRADENTES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1003 - C</t>
+          <t>2720 - C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24/08/2026 08:25</t>
+          <t>24/08/2026 08:21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24/08/2026 08:33</t>
+          <t>24/08/2026 08:32</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46258.35069444445</v>
+        <v>46258.34791666667</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>46258.35625</v>
+        <v>46258.35555555556</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>46258</v>
@@ -740,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17084072</v>
+        <v>17084071</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -774,22 +774,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS - PE</t>
+          <t>422 VILA TORRES PE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Avenida INTERNACIONAL</t>
+          <t>Rua TIRADENTES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>703 - C</t>
+          <t>1003 - C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24/08/2026 08:52</t>
+          <t>24/08/2026 08:25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24/08/2026 09:05</t>
+          <t>24/08/2026 08:33</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="N3" s="2" t="n">
-        <v>46258.36944444444</v>
+        <v>46258.35069444445</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>46258.37847222222</v>
+        <v>46258.35625</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>46258</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1620</v>
+        <v>240</v>
       </c>
       <c r="AB3" t="b">
         <v>0</v>
@@ -878,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17084073</v>
+        <v>17097216</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -917,17 +917,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Avenida INTERNACIONAL</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>510 - 1 - C</t>
+          <t>426 - 2 - C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24/08/2026 09:06</t>
+          <t>24/08/2026 08:39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24/08/2026 09:29</t>
+          <t>24/08/2026 08:54</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>46258.37916666667</v>
+        <v>46258.36041666667</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>46258.39513888889</v>
+        <v>46258.37083333333</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>46258</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
@@ -1013,10 +1013,10 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
-        <v>546</v>
+        <v>519</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17084074</v>
+        <v>17084072</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1050,22 +1050,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA - PE</t>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rua VENCESLAU BRAZ</t>
+          <t>Avenida INTERNACIONAL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>146 - C</t>
+          <t>703 - C</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1080,12 +1080,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>24/08/2026 09:34</t>
+          <t>24/08/2026 08:52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24/08/2026 09:43</t>
+          <t>24/08/2026 09:05</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>46258.39861111111</v>
+        <v>46258.36944444444</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>46258.40486111111</v>
+        <v>46258.37847222222</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>46258</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1680</v>
+        <v>780</v>
       </c>
       <c r="AB5" t="b">
         <v>0</v>
@@ -1151,10 +1151,10 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5" t="n">
-        <v>574</v>
+        <v>532</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1174,6 +1174,420 @@
         <v>1</v>
       </c>
       <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17097217</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Q009</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>703 - C</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>24/08/2026 08:58</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46258.37361111111</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>46258.38263888889</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="R6" t="n">
+        <v>321</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>538</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17084073</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>510 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:29</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46258.37916666667</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>46258.39513888889</v>
+      </c>
+      <c r="P7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="R7" t="n">
+        <v>321</v>
+      </c>
+      <c r="S7" t="n">
+        <v>34</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>546</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17084074</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>413 - BAIRRO DA GRANJA - PE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rua VENCESLAU BRAZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>146 - C</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:34</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24/08/2026 09:43</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46258.39861111111</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>46258.40486111111</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>321</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>574</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/321_pe.xlsx
+++ b/data/semanas/321_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,6 +1588,1666 @@
         <v>1</v>
       </c>
       <c r="AL8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>17113662</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rua CARLOS RONCATTI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>101 - C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25/08/2026 08:35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25/08/2026 08:50</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46259.35763888889</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>46259.36805555555</v>
+      </c>
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R9" t="n">
+        <v>321</v>
+      </c>
+      <c r="S9" t="n">
+        <v>34</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>82860</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>515</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17112433</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rua CARLOS RONCATTI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>101 - C</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25/08/2026 08:49</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:02</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46259.36736111111</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>46259.37638888889</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R10" t="n">
+        <v>321</v>
+      </c>
+      <c r="S10" t="n">
+        <v>34</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>529</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>17112434</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>175 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:14</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46259.37777777778</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>46259.38472222222</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R11" t="n">
+        <v>321</v>
+      </c>
+      <c r="S11" t="n">
+        <v>34</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>544</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17112435</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rua CORONEL PONCE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>04 - OU</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:25</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46259.3875</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>46259.39236111111</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>321</v>
+      </c>
+      <c r="S12" t="n">
+        <v>34</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>558</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17112436</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rua SOILO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>488 - C</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:28</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:38</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>46259.39444444444</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>46259.40138888889</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>34</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>600</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>568</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17113663</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>855 - 2 - C</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25/08/2026 09:44</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>25/08/2026 10:20</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>46259.40555555555</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>46259.43055555555</v>
+      </c>
+      <c r="P14" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R14" t="n">
+        <v>321</v>
+      </c>
+      <c r="S14" t="n">
+        <v>34</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>584</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17126841</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>410 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25/08/2026 14:42</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:05</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46259.6125</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>46259.62847222222</v>
+      </c>
+      <c r="P15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R15" t="n">
+        <v>321</v>
+      </c>
+      <c r="S15" t="n">
+        <v>34</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>17880</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>882</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17125256</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Rua MANOELA VIEIRA SOARES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>999 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:41</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>46259.63472222222</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>46259.65347222222</v>
+      </c>
+      <c r="P16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R16" t="n">
+        <v>321</v>
+      </c>
+      <c r="S16" t="n">
+        <v>34</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1920</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>914</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17126842</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Rua DIAMANTINO LIMA DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>220 - C</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:28</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>46259.63472222222</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>46259.64444444444</v>
+      </c>
+      <c r="P17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R17" t="n">
+        <v>321</v>
+      </c>
+      <c r="S17" t="n">
+        <v>34</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>914</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17126843</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rua Anselmo Soares</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>28 - 1 - OU</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:43</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>46259.64583333334</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>46259.65486111111</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R18" t="n">
+        <v>321</v>
+      </c>
+      <c r="S18" t="n">
+        <v>34</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>930</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17126844</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rua FELISBERTO DO AMARAL CARDINAL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>298 - 2 - C</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:46</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:04</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>46259.65694444445</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>46259.66944444444</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R19" t="n">
+        <v>321</v>
+      </c>
+      <c r="S19" t="n">
+        <v>34</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>946</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17126845</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q006</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rua LINO DO AMARAL CARDINAL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>01 - C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>46259.67083333333</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>46259.67638888889</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R20" t="n">
+        <v>321</v>
+      </c>
+      <c r="S20" t="n">
+        <v>34</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>966</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/321_pe.xlsx
+++ b/data/semanas/321_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2421,7 +2421,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17126841</v>
+        <v>17144819</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2435,17 +2435,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>410 - 1 - C</t>
+          <t>138 - C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25/08/2026 14:42</t>
+          <t>25/08/2026 09:45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25/08/2026 15:05</t>
+          <t>25/08/2026 10:17</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46259.6125</v>
+        <v>46259.40625</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46259.62847222222</v>
+        <v>46259.42847222222</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>46259</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>17880</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -2531,14 +2531,14 @@
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>882</v>
+        <v>585</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH15" t="b">
@@ -2559,7 +2559,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17125256</v>
+        <v>17126841</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL- PE</t>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rua MANOELA VIEIRA SOARES</t>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>999 - 1 - C</t>
+          <t>410 - 1 - C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25/08/2026 15:14</t>
+          <t>25/08/2026 14:42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25/08/2026 15:41</t>
+          <t>25/08/2026 15:05</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46259.63472222222</v>
+        <v>46259.6125</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46259.65347222222</v>
+        <v>46259.62847222222</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>46259</v>
@@ -2659,22 +2659,20 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1920</v>
+        <v>17820</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
       </c>
       <c r="AC16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>914</v>
+        <v>882</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -2699,7 +2697,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17126842</v>
+        <v>17125256</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2713,17 +2711,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua DIAMANTINO LIMA DE OLIVEIRA</t>
+          <t>Rua MANOELA VIEIRA SOARES</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>220 - C</t>
+          <t>999 - 1 - C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2743,7 +2741,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25/08/2026 15:28</t>
+          <t>25/08/2026 15:41</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2763,10 +2761,10 @@
         <v>46259.63472222222</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46259.64444444444</v>
+        <v>46259.65347222222</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>46259</v>
@@ -2784,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
@@ -2799,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="AB17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="b">
         <v>1</v>
@@ -2839,7 +2837,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17126843</v>
+        <v>17126842</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2853,17 +2851,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua DIAMANTINO LIMA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>28 - 1 - OU</t>
+          <t>220 - C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2878,12 +2876,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25/08/2026 15:30</t>
+          <t>25/08/2026 15:14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25/08/2026 15:43</t>
+          <t>25/08/2026 15:28</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2900,13 +2898,13 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>46259.64583333334</v>
+        <v>46259.63472222222</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46259.65486111111</v>
+        <v>46259.64444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>46259</v>
@@ -2939,20 +2937,22 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17126844</v>
+        <v>17126843</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2991,17 +2991,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua FELISBERTO DO AMARAL CARDINAL</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>298 - 2 - C</t>
+          <t>28 - 1 - OU</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25/08/2026 15:46</t>
+          <t>25/08/2026 15:30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25/08/2026 16:04</t>
+          <t>25/08/2026 15:43</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46259.65694444445</v>
+        <v>46259.64583333334</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46259.66944444444</v>
+        <v>46259.65486111111</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>46259</v>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="AF19" t="n">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17126845</v>
+        <v>17126844</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua LINO DO AMARAL CARDINAL</t>
+          <t>Rua FELISBERTO DO AMARAL CARDINAL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01 - C</t>
+          <t>298 - 2 - C</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25/08/2026 16:06</t>
+          <t>25/08/2026 15:46</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25/08/2026 16:14</t>
+          <t>25/08/2026 16:04</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>46259.67083333333</v>
+        <v>46259.65694444445</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46259.67638888889</v>
+        <v>46259.66944444444</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>46259</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="b">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1200</v>
+        <v>960</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -3225,29 +3225,305 @@
       </c>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>946</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17126845</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q006</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rua LINO DO AMARAL CARDINAL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>01 - C</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>46259.67083333333</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>46259.67638888889</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R21" t="n">
+        <v>321</v>
+      </c>
+      <c r="S21" t="n">
+        <v>34</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="n">
         <v>16</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AF21" t="n">
         <v>966</v>
       </c>
-      <c r="AG20" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="AH20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="b">
+      <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17144935</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>410 SALGADO FILHO PE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>273 - C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:06</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:10</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>46260.62916666667</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>46260.63194444445</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="R22" t="n">
+        <v>321</v>
+      </c>
+      <c r="S22" t="n">
+        <v>34</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>82800</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>906</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/321_pe.xlsx
+++ b/data/semanas/321_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17097217</v>
+        <v>17084073</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>703 - C</t>
+          <t>510 - 1 - C</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24/08/2026 08:58</t>
+          <t>24/08/2026 09:06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24/08/2026 09:11</t>
+          <t>24/08/2026 09:29</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46258.37361111111</v>
+        <v>46258.37916666667</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46258.38263888889</v>
+        <v>46258.39513888889</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>46258</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>360</v>
+        <v>840</v>
       </c>
       <c r="AB6" t="b">
         <v>0</v>
@@ -1289,10 +1289,10 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17084073</v>
+        <v>17084074</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1326,22 +1326,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS - PE</t>
+          <t>413 - BAIRRO DA GRANJA - PE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Avenida INTERNACIONAL</t>
+          <t>Rua VENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>510 - 1 - C</t>
+          <t>146 - C</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24/08/2026 09:06</t>
+          <t>24/08/2026 09:34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24/08/2026 09:29</t>
+          <t>24/08/2026 09:43</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46258.37916666667</v>
+        <v>46258.39861111111</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>46258.39513888889</v>
+        <v>46258.40486111111</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>46258</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>480</v>
+        <v>1680</v>
       </c>
       <c r="AB7" t="b">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>9</v>
       </c>
       <c r="AF7" t="n">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17084074</v>
+        <v>17154248</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1464,22 +1464,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA - PE</t>
+          <t>411 - JARDIM AEROPORTO - PE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rua VENCESLAU BRAZ</t>
+          <t>Rua AEROPORTO CONGONHAS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>146 - C</t>
+          <t>535 - C</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24/08/2026 09:34</t>
+          <t>25/08/2026 08:24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24/08/2026 09:43</t>
+          <t>25/08/2026 08:39</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1516,16 +1516,16 @@
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>46258.39861111111</v>
+        <v>46259.35</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46258.40486111111</v>
+        <v>46259.36041666667</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="R8" t="n">
         <v>321</v>
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1680</v>
+        <v>82200</v>
       </c>
       <c r="AB8" t="b">
         <v>0</v>
@@ -1565,10 +1565,10 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>574</v>
+        <v>504</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="b">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>82860</v>
+        <v>660</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -1975,9 +1975,11 @@
         <v>0</v>
       </c>
       <c r="AC11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
@@ -2007,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17112435</v>
+        <v>17154249</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2016,22 +2018,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+          <t>406 - JARDIM PRIMAVERA - PE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Rua VASCO DA GAMA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>04 - OU</t>
+          <t>327 - 5 - C</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2046,12 +2048,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>25/08/2026 09:04</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>25/08/2026 09:18</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>25/08/2026 09:25</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2068,13 +2070,13 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
+        <v>46259.37777777778</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>46259.3875</v>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>46259.39236111111</v>
-      </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>46259</v>
@@ -2107,20 +2109,22 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
       <c r="AE12" t="n">
         <v>9</v>
       </c>
       <c r="AF12" t="n">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2145,7 +2149,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17112436</v>
+        <v>17112435</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2159,17 +2163,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua SOILO DE FREITAS</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>488 - C</t>
+          <t>04 - OU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2184,12 +2188,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25/08/2026 09:28</t>
+          <t>25/08/2026 09:18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25/08/2026 09:38</t>
+          <t>25/08/2026 09:25</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2206,13 +2210,13 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>46259.39444444444</v>
+        <v>46259.3875</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46259.40138888889</v>
+        <v>46259.39236111111</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>46259</v>
@@ -2245,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="AB13" t="b">
         <v>0</v>
@@ -2258,7 +2262,7 @@
         <v>9</v>
       </c>
       <c r="AF13" t="n">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2283,7 +2287,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17113663</v>
+        <v>17154250</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2292,22 +2296,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+          <t>405 - ALTOS DA GLORIA - PE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+          <t>Rua JOÃO BREMBATI CALVOSO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>855 - 2 - C</t>
+          <t>464 - OU</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2322,12 +2326,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25/08/2026 09:44</t>
+          <t>25/08/2026 09:26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25/08/2026 10:20</t>
+          <t>25/08/2026 09:40</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2344,13 +2348,13 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>46259.40555555555</v>
+        <v>46259.39305555556</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>46259.43055555555</v>
+        <v>46259.40277777778</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>46259</v>
@@ -2365,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
@@ -2383,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>960</v>
+        <v>480</v>
       </c>
       <c r="AB14" t="b">
         <v>0</v>
@@ -2396,7 +2400,7 @@
         <v>9</v>
       </c>
       <c r="AF14" t="n">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2421,7 +2425,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17144819</v>
+        <v>17112436</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2430,22 +2434,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+          <t>Rua SOILO DE FREITAS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>138 - C</t>
+          <t>488 - C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2460,12 +2464,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25/08/2026 09:45</t>
+          <t>25/08/2026 09:28</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25/08/2026 10:17</t>
+          <t>25/08/2026 09:38</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2482,13 +2486,13 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46259.40625</v>
+        <v>46259.39444444444</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46259.42847222222</v>
+        <v>46259.40138888889</v>
       </c>
       <c r="P15" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>46259</v>
@@ -2503,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
@@ -2521,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -2534,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -2559,7 +2563,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17126841</v>
+        <v>17113663</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2573,17 +2577,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>410 - 1 - C</t>
+          <t>855 - 2 - C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2598,12 +2602,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25/08/2026 14:42</t>
+          <t>25/08/2026 09:44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25/08/2026 15:05</t>
+          <t>25/08/2026 10:20</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2620,13 +2624,13 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46259.6125</v>
+        <v>46259.40555555555</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46259.62847222222</v>
+        <v>46259.43055555555</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>46259</v>
@@ -2641,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2659,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>17820</v>
+        <v>960</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
@@ -2669,14 +2673,14 @@
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
-        <v>882</v>
+        <v>584</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH16" t="b">
@@ -2697,7 +2701,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17125256</v>
+        <v>17144819</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2706,22 +2710,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL- PE</t>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua MANOELA VIEIRA SOARES</t>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>999 - 1 - C</t>
+          <t>138 - C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2736,12 +2740,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25/08/2026 15:14</t>
+          <t>25/08/2026 09:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25/08/2026 15:41</t>
+          <t>25/08/2026 10:17</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2758,13 +2762,13 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>46259.63472222222</v>
+        <v>46259.40625</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46259.65347222222</v>
+        <v>46259.42847222222</v>
       </c>
       <c r="P17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>46259</v>
@@ -2779,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2797,26 +2801,24 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1920</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
       </c>
       <c r="AC17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF17" t="n">
-        <v>914</v>
+        <v>585</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH17" t="b">
@@ -2837,7 +2839,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17126842</v>
+        <v>17154251</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2846,22 +2848,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL- PE</t>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rua DIAMANTINO LIMA DE OLIVEIRA</t>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>220 - C</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2876,12 +2878,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25/08/2026 15:14</t>
+          <t>25/08/2026 09:47</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25/08/2026 15:28</t>
+          <t>25/08/2026 10:07</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2898,13 +2900,13 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>46259.63472222222</v>
+        <v>46259.40763888889</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>46259.64444444444</v>
+        <v>46259.42152777778</v>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>46259</v>
@@ -2922,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
@@ -2937,26 +2939,24 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF18" t="n">
-        <v>914</v>
+        <v>587</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH18" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17126843</v>
+        <v>17126841</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2986,22 +2986,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL- PE</t>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28 - 1 - OU</t>
+          <t>410 - 1 - C</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25/08/2026 15:30</t>
+          <t>25/08/2026 14:42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25/08/2026 15:43</t>
+          <t>25/08/2026 15:05</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>46259.64583333334</v>
+        <v>46259.6125</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>46259.65486111111</v>
+        <v>46259.62847222222</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>46259</v>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>960</v>
+        <v>17700</v>
       </c>
       <c r="AB19" t="b">
         <v>0</v>
@@ -3087,10 +3087,10 @@
       </c>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>930</v>
+        <v>882</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17126844</v>
+        <v>17154252</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3129,17 +3129,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rua FELISBERTO DO AMARAL CARDINAL</t>
+          <t>Rodovia BR 463</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>298 - 2 - C</t>
+          <t>2667 - 2 - C</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25/08/2026 15:46</t>
+          <t>25/08/2026 15:13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25/08/2026 16:04</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>46259.65694444445</v>
+        <v>46259.63402777778</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>46259.66944444444</v>
+        <v>46259.66319444445</v>
       </c>
       <c r="P20" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>46259</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
         <v>1</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>960</v>
+        <v>1860</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -3228,7 +3228,7 @@
         <v>15</v>
       </c>
       <c r="AF20" t="n">
-        <v>946</v>
+        <v>913</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17126845</v>
+        <v>17125256</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3267,17 +3267,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rua LINO DO AMARAL CARDINAL</t>
+          <t>Rua MANOELA VIEIRA SOARES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01 - C</t>
+          <t>999 - 1 - C</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25/08/2026 16:06</t>
+          <t>25/08/2026 15:14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25/08/2026 16:14</t>
+          <t>25/08/2026 15:41</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="N21" s="2" t="n">
-        <v>46259.67083333333</v>
+        <v>46259.63472222222</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>46259.67638888889</v>
+        <v>46259.65347222222</v>
       </c>
       <c r="P21" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>46259</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
@@ -3353,20 +3353,22 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
       </c>
       <c r="AC21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2</v>
+      </c>
       <c r="AE21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
-        <v>966</v>
+        <v>914</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3391,7 +3393,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17144935</v>
+        <v>17126842</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3400,22 +3402,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>410 SALGADO FILHO PE</t>
+          <t>400 - JULIA CARDINAL- PE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+          <t>Rua DIAMANTINO LIMA DE OLIVEIRA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>273 - C</t>
+          <t>220 - C</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3430,12 +3432,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>26/08/2026 15:06</t>
+          <t>25/08/2026 15:14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26/08/2026 15:10</t>
+          <t>25/08/2026 15:28</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -3452,16 +3454,16 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>46260.62916666667</v>
+        <v>46259.63472222222</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>46260.63194444445</v>
+        <v>46259.64444444444</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="R22" t="n">
         <v>321</v>
@@ -3491,39 +3493,1697 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>82800</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
+        <v>914</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>17126843</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Rua Anselmo Soares</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>28 - 1 - OU</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:30</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:43</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>46259.64583333334</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>46259.65486111111</v>
+      </c>
+      <c r="P23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R23" t="n">
+        <v>321</v>
+      </c>
+      <c r="S23" t="n">
+        <v>34</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>930</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>17126844</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rua FELISBERTO DO AMARAL CARDINAL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>298 - 2 - C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25/08/2026 15:46</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:04</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>46259.65694444445</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>46259.66944444444</v>
+      </c>
+      <c r="P24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R24" t="n">
+        <v>321</v>
+      </c>
+      <c r="S24" t="n">
+        <v>34</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>960</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>946</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>17126845</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q006</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rua LINO DO AMARAL CARDINAL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>01 - C</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:06</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>46259.67083333333</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>46259.67638888889</v>
+      </c>
+      <c r="P25" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="R25" t="n">
+        <v>321</v>
+      </c>
+      <c r="S25" t="n">
+        <v>34</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>966</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>17144935</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>410 SALGADO FILHO PE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>273 - C</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:06</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>26/08/2026 15:10</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>46260.62916666667</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>46260.63194444445</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="R26" t="n">
+        <v>321</v>
+      </c>
+      <c r="S26" t="n">
+        <v>34</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>82800</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF26" t="n">
         <v>906</v>
       </c>
-      <c r="AG22" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="AH22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2</v>
       </c>
-      <c r="AJ22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="b">
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>17164831</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Rodovia BR 463</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>09 - C</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>27/08/2026 08:56</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>27/08/2026 09:39</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>46261.37222222222</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>46261.40208333333</v>
+      </c>
+      <c r="P27" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R27" t="n">
+        <v>321</v>
+      </c>
+      <c r="S27" t="n">
+        <v>34</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>64200</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>536</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>17164832</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>99 - 3 - C</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>27/08/2026 09:47</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>27/08/2026 10:06</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46261.40763888889</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>46261.42083333333</v>
+      </c>
+      <c r="P28" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R28" t="n">
+        <v>321</v>
+      </c>
+      <c r="S28" t="n">
+        <v>34</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3060</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>587</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>17164833</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2663 - C</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>27/08/2026 10:10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>27/08/2026 10:25</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>46261.42361111111</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>46261.43402777778</v>
+      </c>
+      <c r="P29" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R29" t="n">
+        <v>321</v>
+      </c>
+      <c r="S29" t="n">
+        <v>34</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>610</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17170606</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rua 18 DE JULHO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>240 - C</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:01</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:11</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46261.58402777778</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>46261.59097222222</v>
+      </c>
+      <c r="P30" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R30" t="n">
+        <v>321</v>
+      </c>
+      <c r="S30" t="n">
+        <v>34</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>13860</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>841</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>17170818</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2577 - C</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:34</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>46261.59861111111</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>46261.60694444444</v>
+      </c>
+      <c r="P31" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R31" t="n">
+        <v>321</v>
+      </c>
+      <c r="S31" t="n">
+        <v>34</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1260</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>862</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>17170819</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>266 - C</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:37</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>27/08/2026 14:53</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>46261.60902777778</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>46261.62013888889</v>
+      </c>
+      <c r="P32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R32" t="n">
+        <v>321</v>
+      </c>
+      <c r="S32" t="n">
+        <v>34</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>877</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>17169291</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avenida NATALICIO ANTUNES DA SILVA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>270 - 5 - OU</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:06</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:19</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>46261.62916666667</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>46261.63819444444</v>
+      </c>
+      <c r="P33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R33" t="n">
+        <v>321</v>
+      </c>
+      <c r="S33" t="n">
+        <v>34</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>906</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17169292</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Rodovia BR 463</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>08 - C</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>27/08/2026 15:36</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>46261.64236111111</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>46261.65</v>
+      </c>
+      <c r="P34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="R34" t="n">
+        <v>321</v>
+      </c>
+      <c r="S34" t="n">
+        <v>34</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1140</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>925</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="b">
         <v>0</v>
       </c>
     </row>
